--- a/Day-15-Sales-Analysis-Project/Day-15-Sales-Analysis-Project.xlsx
+++ b/Day-15-Sales-Analysis-Project/Day-15-Sales-Analysis-Project.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\90_Day_Data_Analytics\Day-15-Sales-Analysis-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D03C5088-4572-4F6C-BB3E-40DEE85F0092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8814C00B-2571-4520-88C9-AAE5150E39BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" activeTab="2" xr2:uid="{0950D702-5685-449F-814E-BC21922413ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" activeTab="1" xr2:uid="{0950D702-5685-449F-814E-BC21922413ED}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Pivot Table" sheetId="2" r:id="rId2"/>
     <sheet name="Dashboard" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -149,7 +149,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="_ [$₹-4009]\ * #,##0_ ;_ [$₹-4009]\ * \-#,##0_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0_ ;_ [$₹-4009]\ * \-#,##0_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -202,20 +202,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -365,49 +365,7 @@
           <a:sp3d/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -911,8 +869,7 @@
           <a:sp3d/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -955,6 +912,174 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:sp3d/>
+        </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:view3D>
@@ -1105,6 +1230,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-272A-41B3-83CA-8DBBFADCA034}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1148,6 +1278,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-272A-41B3-83CA-8DBBFADCA034}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1191,6 +1326,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-272A-41B3-83CA-8DBBFADCA034}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -5546,7 +5686,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Kunal Das" refreshedDate="46107.518495717595" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{BF45FCB1-D2D3-4241-A57C-7FA0F0D02CEB}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:E11" sheet="Sheet1"/>
+    <worksheetSource ref="A1:E11" sheet="Data"/>
   </cacheSource>
   <cacheFields count="5">
     <cacheField name="Order_ID" numFmtId="0">
@@ -5562,7 +5702,7 @@
         <s v="Furniture"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Sales" numFmtId="171">
+    <cacheField name="Sales" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2500" maxValue="55000"/>
     </cacheField>
     <cacheField name="Region" numFmtId="0">
@@ -5658,7 +5798,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3661A50F-EBA1-4416-996A-69266833D217}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3661A50F-EBA1-4416-996A-69266833D217}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
   <location ref="B12:C17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -5671,7 +5811,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" numFmtId="171" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="0"/>
@@ -5708,7 +5848,7 @@
   <dataFields count="1">
     <dataField name="Sum of Sales" fld="3" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
-  <chartFormats count="7">
+  <chartFormats count="11">
     <chartFormat chart="12" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -5784,6 +5924,54 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="15" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -5798,7 +5986,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{385F6AA0-5224-4378-AC5E-F29299ECC413}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{385F6AA0-5224-4378-AC5E-F29299ECC413}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
   <location ref="B3:C7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -5811,7 +5999,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" numFmtId="171" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -5835,7 +6023,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Sales" fld="3" baseField="0" baseItem="0" numFmtId="171"/>
+    <dataField name="Sum of Sales" fld="3" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <chartFormats count="2">
     <chartFormat chart="7" format="0" series="1">
